--- a/Data/predictions_ranger_filtered_kefir.xlsx
+++ b/Data/predictions_ranger_filtered_kefir.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="17">
   <si>
     <t>pH_original</t>
   </si>
@@ -49,18 +49,6 @@
     <t>x_interval_width</t>
   </si>
   <si>
-    <t>0_min</t>
-  </si>
-  <si>
-    <t>5_min</t>
-  </si>
-  <si>
-    <t>10_min</t>
-  </si>
-  <si>
-    <t>15_min</t>
-  </si>
-  <si>
     <t>Time</t>
   </si>
   <si>
@@ -74,6 +62,9 @@
   </si>
   <si>
     <t>RT</t>
+  </si>
+  <si>
+    <t>Temp</t>
   </si>
 </sst>
 </file>
@@ -434,9 +425,12 @@
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -474,11 +468,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
+      <c r="A2" s="2">
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3">
         <v>25</v>
@@ -518,11 +512,11 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
+      <c r="A3" s="2">
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C3" s="4">
         <v>25</v>
@@ -562,11 +556,11 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="2">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
       </c>
       <c r="C4" s="4">
         <v>25</v>
@@ -606,11 +600,11 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
+      <c r="A5" s="2">
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4">
         <v>25</v>
@@ -650,11 +644,11 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
+      <c r="A6" s="2">
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3">
         <v>13</v>
@@ -694,11 +688,11 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
+      <c r="A7" s="2">
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3">
         <v>13</v>
@@ -738,11 +732,11 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="2">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
       </c>
       <c r="C8" s="3">
         <v>13</v>
@@ -782,11 +776,11 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
+      <c r="A9" s="2">
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3">
         <v>13</v>
@@ -830,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>4.5</v>
@@ -874,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>4.5</v>
@@ -918,10 +912,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>4.3</v>
@@ -962,10 +956,10 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -1006,10 +1000,10 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>3.8</v>
@@ -1050,10 +1044,10 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>3.7</v>
@@ -1094,10 +1088,10 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>3.6</v>
@@ -1138,10 +1132,10 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>3.5</v>
